--- a/resources/reselling/files/reselling-basics-records-ledger.xlsx
+++ b/resources/reselling/files/reselling-basics-records-ledger.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,12 +148,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -523,7 +517,7 @@
   <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -538,8 +532,8 @@
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Records ledger + audit — one row per item (Basics, ch7-9)</t>
         </is>
@@ -559,7 +553,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1">
+    <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Item</t>
@@ -585,7 +579,7 @@
           <t>List $</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Predicted net $</t>
         </is>
@@ -1105,9 +1099,9 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
